--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486504_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486504_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4661</v>
+        <v>5.6379</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1507</v>
+        <v>6.8465</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6846</v>
+        <v>-1.2086</v>
       </c>
       <c r="G2" t="n">
         <v>8.060600000000001</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1595</v>
+        <v>0.0123</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8904</v>
+        <v>-0.1947</v>
       </c>
       <c r="U2" t="n">
-        <v>0.731</v>
+        <v>0.207</v>
       </c>
       <c r="V2" t="n">
         <v>-1.13</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7384</v>
+        <v>2.3171</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5803</v>
+        <v>1.4585</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1581</v>
+        <v>0.8586</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8051</v>
+        <v>-0.6505</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0888</v>
+        <v>2.6915</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2837</v>
+        <v>-3.342</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6953</v>
+        <v>0.4397</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0251</v>
+        <v>2.4454</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6702</v>
+        <v>-2.0057</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8902</v>
+        <v>-1.0902</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0636</v>
+        <v>0.2461</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9539</v>
+        <v>-1.3364</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7158</v>
+        <v>-0.3151</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2776</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4382</v>
+        <v>-0.2262</v>
       </c>
       <c r="V3" t="n">
+        <v>1.3252</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.3252</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.716</v>
+        <v>1.8696</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0115</v>
+        <v>1.1102</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7045</v>
+        <v>0.7595</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6505</v>
+        <v>0.7911</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6915</v>
+        <v>-0.3986</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.342</v>
+        <v>1.1897</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4397</v>
+        <v>2.1244</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4454</v>
+        <v>0.3832</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.0057</v>
+        <v>1.7412</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0902</v>
+        <v>-1.3333</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2461</v>
+        <v>-0.7819</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3364</v>
+        <v>-0.5514</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9163</v>
+        <v>0.6435</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.536</v>
+        <v>0.0733</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3803</v>
+        <v>0.5702</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6508</v>
+        <v>1.7474</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7064</v>
+        <v>1.246</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9444</v>
+        <v>0.5014</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7911</v>
+        <v>-1.3928</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3986</v>
+        <v>1.2105</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1897</v>
+        <v>-2.6033</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1244</v>
+        <v>0.2823</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3832</v>
+        <v>0.6998</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7412</v>
+        <v>-0.4175</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3333</v>
+        <v>-1.6751</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7819</v>
+        <v>0.5107</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5514</v>
+        <v>-2.1858</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>-0.435</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-2.6101</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4247</v>
+        <v>0.1854</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3305</v>
+        <v>0.1839</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7551</v>
+        <v>0.0015</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3.3899</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.3899</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5295</v>
+        <v>1.5594</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9973</v>
+        <v>1.4938</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5322</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3928</v>
+        <v>0.8051</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2105</v>
+        <v>1.0888</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.6033</v>
+        <v>-0.2837</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2823</v>
+        <v>1.6953</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6998</v>
+        <v>1.0251</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4175</v>
+        <v>0.6702</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6751</v>
+        <v>-0.8902</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5107</v>
+        <v>0.0636</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1858</v>
+        <v>-0.9539</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.6101</v>
+        <v>-1.5225</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0326</v>
+        <v>0.5369</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0649</v>
+        <v>0.1911</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0323</v>
+        <v>0.3458</v>
       </c>
       <c r="V6" t="n">
-        <v>3.3899</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3899</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3915</v>
+        <v>1.2981</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7022</v>
+        <v>1.5472</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3107</v>
+        <v>-0.2491</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1511</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5001</v>
+        <v>0.4068</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2656</v>
+        <v>0.1106</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2346</v>
+        <v>0.2962</v>
       </c>
       <c r="V7" t="n">
         <v>2.2599</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5391</v>
+        <v>0.3206</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5354</v>
+        <v>1.0703</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9963</v>
+        <v>-0.7497</v>
       </c>
       <c r="G8" t="n">
         <v>0.5219</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6475</v>
+        <v>0.429</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7367</v>
+        <v>0.2716</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0892</v>
+        <v>0.1574</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1952</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4371</v>
+        <v>-1.0006</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3713</v>
+        <v>-0.0073</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8084</v>
+        <v>-0.9933</v>
       </c>
       <c r="G9" t="n">
         <v>0.5111</v>
@@ -1156,13 +1156,13 @@
         <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7467</v>
+        <v>0.1833</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4831</v>
+        <v>0.1046</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2636</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-1.695</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3541</v>
+        <v>-1.5362</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9126</v>
+        <v>0.4223</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2667</v>
+        <v>-1.9585</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3304</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1286</v>
+        <v>-0.0535</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6682</v>
+        <v>0.1779</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5396</v>
+        <v>-0.2313</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9347</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7609</v>
+        <v>-2.0912</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4639</v>
+        <v>0.0517</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.297</v>
+        <v>-2.1429</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4166</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1268</v>
+        <v>0.5429</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3425</v>
+        <v>0.173</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2157</v>
+        <v>0.3698</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5649999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1915</v>
+        <v>-3.807</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8503</v>
+        <v>-3.5583</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3412</v>
+        <v>-0.2487</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6006</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1559</v>
+        <v>0.2286</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.411</v>
+        <v>-0.119</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2551</v>
+        <v>0.3476</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.287799999999999</v>
+        <v>6.315099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>10.6535</v>
+        <v>11.6809</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.365699999999999</v>
+        <v>-5.3657</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1478</v>
+        <v>2.147800000000001</v>
       </c>
       <c r="H13" t="n">
         <v>9.275399999999998</v>
@@ -1468,13 +1468,13 @@
         <v>14.1378</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7723</v>
+        <v>2.8001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1441</v>
+        <v>0.8834</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9165</v>
+        <v>1.9167</v>
       </c>
       <c r="V13" t="n">
         <v>2.4551</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3561</v>
+        <v>4.5295</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8155</v>
+        <v>2.9272</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5407</v>
+        <v>1.6023</v>
       </c>
       <c r="G14" t="n">
         <v>2.8083</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0394</v>
+        <v>0.134</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0769</v>
+        <v>0.0349</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0375</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0.9347</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. POLYNICE</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6697</v>
+        <v>3.5091</v>
       </c>
       <c r="E15" t="n">
-        <v>2.331</v>
+        <v>2.6453</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3387</v>
+        <v>0.8638</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6825</v>
+        <v>2.1175</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.2531</v>
+        <v>0.3134</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9356</v>
+        <v>1.8041</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2723</v>
+        <v>2.9902</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.7877</v>
+        <v>1.2108</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0599</v>
+        <v>1.7794</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5898</v>
+        <v>-0.8727</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4654</v>
+        <v>-0.8974</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1243</v>
+        <v>0.0247</v>
       </c>
       <c r="P15" t="n">
         <v>1.9576</v>
@@ -1624,28 +1624,28 @@
         <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7898</v>
+        <v>-0.3707</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2762</v>
+        <v>-0.1274</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5135999999999999</v>
+        <v>-0.2434</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7602</v>
+        <v>-0.1952</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7602</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>C. POLYNICE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9774</v>
+        <v>2.5907</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4218</v>
+        <v>1.4369</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5556</v>
+        <v>1.1537</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1175</v>
+        <v>0.6825</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3134</v>
+        <v>-2.2531</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8041</v>
+        <v>2.9356</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9902</v>
+        <v>1.2723</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2108</v>
+        <v>-1.7877</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7794</v>
+        <v>3.0599</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8727</v>
+        <v>-0.5898</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8974</v>
+        <v>-0.4654</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0247</v>
+        <v>-0.1243</v>
       </c>
       <c r="P16" t="n">
         <v>1.9576</v>
@@ -1702,22 +1702,22 @@
         <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9025</v>
+        <v>0.7108</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3509</v>
+        <v>0.3822</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5516</v>
+        <v>0.3287</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1952</v>
+        <v>-0.7602</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1952</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8265</v>
+        <v>1.6396</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9726</v>
+        <v>1.7549</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1461</v>
+        <v>-0.1153</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0178</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.0604</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8904</v>
+        <v>-0.1081</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0169</v>
+        <v>0.0478</v>
       </c>
       <c r="V17" t="n">
         <v>0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1591</v>
+        <v>0.5432</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1717</v>
+        <v>2.2834</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0125</v>
+        <v>-1.7402</v>
       </c>
       <c r="G18" t="n">
         <v>1.1824</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0859</v>
+        <v>-0.7018</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5732</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4009</v>
+        <v>-0.1286</v>
       </c>
       <c r="V18" t="n">
         <v>2.4552</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.28</v>
+        <v>-0.8439</v>
       </c>
       <c r="E19" t="n">
-        <v>1.075</v>
+        <v>0.5162</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3549</v>
+        <v>-1.3601</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2806</v>
@@ -1936,13 +1936,13 @@
         <v>2.3926</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0653</v>
+        <v>0.5014</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6682</v>
+        <v>0.1094</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3972</v>
+        <v>0.392</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3698</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2146</v>
+        <v>-0.9101</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6711</v>
+        <v>-1.3358</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4565</v>
+        <v>0.4257</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3995</v>
@@ -2014,13 +2014,13 @@
         <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0326</v>
+        <v>0.2719</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.274</v>
+        <v>0.0613</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2414</v>
+        <v>0.2106</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9548</v>
+        <v>-3.4783</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0598</v>
+        <v>0.1715</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.0146</v>
+        <v>-3.6498</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7715</v>
@@ -2092,13 +2092,13 @@
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2057</v>
+        <v>-0.7291</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.822</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3837</v>
+        <v>-0.0189</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3252</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.7701</v>
+        <v>-6.0333</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7995</v>
+        <v>-2.6877</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9706</v>
+        <v>-3.3456</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1997</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1354</v>
+        <v>-0.3987</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.6417</v>
       </c>
       <c r="U22" t="n">
-        <v>0.618</v>
+        <v>0.243</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.057</v>
+        <v>-6.0891</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0109</v>
+        <v>-2.3462</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.046</v>
+        <v>-3.7429</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2693</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3527</v>
+        <v>-0.3848</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.3437</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3443</v>
+        <v>-0.0412</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2599</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.287700000000001</v>
+        <v>-4.542600000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>5.365900000000002</v>
+        <v>5.365699999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.6532</v>
+        <v>-9.9084</v>
       </c>
       <c r="G24" t="n">
         <v>-2.147699999999999</v>
@@ -2326,13 +2326,13 @@
         <v>15.2255</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7726</v>
+        <v>-1.0274</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.9167</v>
+        <v>-1.9165</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1441</v>
+        <v>0.8891</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4552</v>
